--- a/documents/ParaBank_Test_Cases.xlsx
+++ b/documents/ParaBank_Test_Cases.xlsx
@@ -1,42 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DVDSTORE\Desktop\Rawad files\My Own Files\project\qa-project\bank.system\documents\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31A51F0-89E3-47F8-AA84-500F782A21C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Homepage" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Login" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Registration" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Header Links" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Footer Links" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="About Us" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Services" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Contact Us" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Admin Page" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Products (External)" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Locations (External)" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Forum (External)" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Parasoft Main Site (External)" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Homepage" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="2" r:id="rId2"/>
+    <sheet name="Registration" sheetId="3" r:id="rId3"/>
+    <sheet name="Header Links" sheetId="4" r:id="rId4"/>
+    <sheet name="Footer Links" sheetId="5" r:id="rId5"/>
+    <sheet name="About Us" sheetId="6" r:id="rId6"/>
+    <sheet name="Services" sheetId="7" r:id="rId7"/>
+    <sheet name="Contact Us" sheetId="8" r:id="rId8"/>
+    <sheet name="Admin Page" sheetId="9" r:id="rId9"/>
+    <sheet name="Products (External)" sheetId="10" r:id="rId10"/>
+    <sheet name="Locations (External)" sheetId="11" r:id="rId11"/>
+    <sheet name="Forum (External)" sheetId="12" r:id="rId12"/>
+    <sheet name="Parasoft Main Site (External)" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'About Us'!$A$1:$I$7</definedName>
-    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'Admin Page'!$A$1:$I$9</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'Contact Us'!$A$1:$I$8</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Footer Links'!$A$1:$I$12</definedName>
-    <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">'Forum (External)'!$A$1:$I$7</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Header Links'!$A$1:$I$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Homepage!$A$1:$I$11</definedName>
-    <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">'Locations (External)'!$A$1:$I$6</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Login!$A$1:$I$11</definedName>
-    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'Parasoft Main Site (External)'!$A$1:$I$7</definedName>
-    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'Products (External)'!$A$1:$I$6</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Services!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'About Us'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Admin Page'!$A$1:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Contact Us'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Footer Links'!$A$1:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Forum (External)'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Header Links'!$A$1:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Homepage!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Locations (External)'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Login!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Parasoft Main Site (External)'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Products (External)'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Services!$A$1:$I$8</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -48,1728 +53,1725 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="554">
   <si>
-    <t xml:space="preserve">TC ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Case Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Steps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Locator(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homepage loads successfully</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Browser open, no prior session</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to https://parabank.parasoft.com/parabank/index.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page loads (HTTP 200); title equals 'ParaBank | Welcome | Online Banking'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">driver.getTitle(); By.tagName("body")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HP-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ParaBank logo is visible and links home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homepage loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate logo image
+    <t>TC ID</t>
+  </si>
+  <si>
+    <t>Test Case Title</t>
+  </si>
+  <si>
+    <t>Preconditions</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Locator(s)</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>TC-HP-01</t>
+  </si>
+  <si>
+    <t>Homepage loads successfully</t>
+  </si>
+  <si>
+    <t>Browser open, no prior session</t>
+  </si>
+  <si>
+    <t>1. Navigate to https://parabank.parasoft.com/parabank/index.htm</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Page loads (HTTP 200); title equals 'ParaBank | Welcome | Online Banking'</t>
+  </si>
+  <si>
+    <t>driver.getTitle(); By.tagName("body")</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>TC-HP-02</t>
+  </si>
+  <si>
+    <t>ParaBank logo is visible and links home</t>
+  </si>
+  <si>
+    <t>Homepage loaded</t>
+  </si>
+  <si>
+    <t>1. Locate logo image
 2. Click logo</t>
   </si>
   <si>
-    <t xml:space="preserve">Logo is visible; clicking it reloads/stays on index.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector("a img[alt='ParaBank']")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HP-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Login panel is present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate Username field
+    <t>Logo is visible; clicking it reloads/stays on index.htm</t>
+  </si>
+  <si>
+    <t>By.cssSelector("a img[alt='ParaBank']")</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>TC-HP-03</t>
+  </si>
+  <si>
+    <t>Customer Login panel is present</t>
+  </si>
+  <si>
+    <t>1. Locate Username field
 2. Locate Password field
 3. Locate Log In button</t>
   </si>
   <si>
-    <t xml:space="preserve">Username field, Password field and 'Log In' button are all visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.name("username"); By.name("password"); By.cssSelector("input[value='Log In']")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HP-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Forgot login info?' link is visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate link under login panel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link is visible with text 'Forgot login info?'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Forgot login info?")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HP-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Register' link is visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link is visible with text 'Register'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Register")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HP-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latest News panel renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Latest News' section
+    <t>Username field, Password field and 'Log In' button are all visible</t>
+  </si>
+  <si>
+    <t>By.name("username"); By.name("password"); By.cssSelector("input[value='Log In']")</t>
+  </si>
+  <si>
+    <t>TC-HP-04</t>
+  </si>
+  <si>
+    <t>'Forgot login info?' link is visible</t>
+  </si>
+  <si>
+    <t>1. Locate link under login panel</t>
+  </si>
+  <si>
+    <t>Link is visible with text 'Forgot login info?'</t>
+  </si>
+  <si>
+    <t>By.linkText("Forgot login info?")</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TC-HP-05</t>
+  </si>
+  <si>
+    <t>'Register' link is visible</t>
+  </si>
+  <si>
+    <t>Link is visible with text 'Register'</t>
+  </si>
+  <si>
+    <t>By.linkText("Register")</t>
+  </si>
+  <si>
+    <t>TC-HP-06</t>
+  </si>
+  <si>
+    <t>Latest News panel renders</t>
+  </si>
+  <si>
+    <t>1. Locate 'Latest News' section
 2. Verify at least 1 dated news item</t>
   </si>
   <si>
-    <t xml:space="preserve">At least one news entry with a date is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//h2[contains(text(),'Latest News')]/following::ul[1]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HP-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATM Services panel renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'ATM Services' panel
+    <t>At least one news entry with a date is displayed</t>
+  </si>
+  <si>
+    <t>By.xpath("//h2[contains(text(),'Latest News')]/following::ul[1]")</t>
+  </si>
+  <si>
+    <t>TC-HP-07</t>
+  </si>
+  <si>
+    <t>ATM Services panel renders</t>
+  </si>
+  <si>
+    <t>1. Locate 'ATM Services' panel
 2. Verify list items</t>
   </si>
   <si>
-    <t xml:space="preserve">Withdraw Funds, Transfer Funds, Check Balances, Make Deposits are listed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'ATM Services')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HP-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online Services panel renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Online Services' panel
+    <t>Withdraw Funds, Transfer Funds, Check Balances, Make Deposits are listed</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'ATM Services')]")</t>
+  </si>
+  <si>
+    <t>TC-HP-08</t>
+  </si>
+  <si>
+    <t>Online Services panel renders</t>
+  </si>
+  <si>
+    <t>1. Locate 'Online Services' panel
 2. Verify list items</t>
   </si>
   <si>
-    <t xml:space="preserve">Bill Pay, Account History, Transfer Funds are listed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'Online Services')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HP-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary top navigation bar is present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify Solutions, About Us, Services, Products, Locations, Admin Page links all render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All 6 nav items are visible in the header</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("headerPanel")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HP-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secondary nav (home/about/contact) is present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify home, about, contact links render below header</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All 3 links are visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("home"); By.linkText("about"); By.linkText("contact")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid login succeeds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registered customer account exists; homepage loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter valid username
+    <t>Bill Pay, Account History, Transfer Funds are listed</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'Online Services')]")</t>
+  </si>
+  <si>
+    <t>TC-HP-09</t>
+  </si>
+  <si>
+    <t>Primary top navigation bar is present</t>
+  </si>
+  <si>
+    <t>1. Verify Solutions, About Us, Services, Products, Locations, Admin Page links all render</t>
+  </si>
+  <si>
+    <t>All 6 nav items are visible in the header</t>
+  </si>
+  <si>
+    <t>By.id("headerPanel")</t>
+  </si>
+  <si>
+    <t>TC-HP-10</t>
+  </si>
+  <si>
+    <t>Secondary nav (home/about/contact) is present</t>
+  </si>
+  <si>
+    <t>1. Verify home, about, contact links render below header</t>
+  </si>
+  <si>
+    <t>All 3 links are visible</t>
+  </si>
+  <si>
+    <t>By.linkText("home"); By.linkText("about"); By.linkText("contact")</t>
+  </si>
+  <si>
+    <t>TC-LOG-01</t>
+  </si>
+  <si>
+    <t>Valid login succeeds</t>
+  </si>
+  <si>
+    <t>Registered customer account exists; homepage loaded</t>
+  </si>
+  <si>
+    <t>1. Enter valid username
 2. Enter valid password
 3. Click Log In</t>
   </si>
   <si>
-    <t xml:space="preserve">username=john / password=demo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redirected to accounts overview page; 'Welcome &lt;name&gt;' and 'Log Out' shown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOG-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login fails with invalid username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter invalid username
+    <t>username=john / password=demo</t>
+  </si>
+  <si>
+    <t>Redirected to accounts overview page; 'Welcome &lt;name&gt;' and 'Log Out' shown</t>
+  </si>
+  <si>
+    <t>TC-LOG-02</t>
+  </si>
+  <si>
+    <t>Login fails with invalid username</t>
+  </si>
+  <si>
+    <t>1. Enter invalid username
 2. Enter any password
 3. Click Log In</t>
   </si>
   <si>
-    <t xml:space="preserve">username=invalidUser / password=demo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error message displayed: 'The username and password could not be verified.'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.name("username"); By.name("password"); By.cssSelector("input[value='Log In']"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOG-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login fails with invalid password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter valid username
+    <t>username=invalidUser / password=demo</t>
+  </si>
+  <si>
+    <t>Error message displayed: 'The username and password could not be verified.'</t>
+  </si>
+  <si>
+    <t>By.name("username"); By.name("password"); By.cssSelector("input[value='Log In']"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-LOG-03</t>
+  </si>
+  <si>
+    <t>Login fails with invalid password</t>
+  </si>
+  <si>
+    <t>1. Enter valid username
 2. Enter incorrect password
 3. Click Log In</t>
   </si>
   <si>
-    <t xml:space="preserve">username=john / password=wrongpass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error message displayed; user stays on login page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.name("username"); By.name("password"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOG-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login fails with empty username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Leave username blank
+    <t>username=john / password=wrongpass</t>
+  </si>
+  <si>
+    <t>Error message displayed; user stays on login page</t>
+  </si>
+  <si>
+    <t>By.name("username"); By.name("password"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-LOG-04</t>
+  </si>
+  <si>
+    <t>Login fails with empty username</t>
+  </si>
+  <si>
+    <t>1. Leave username blank
 2. Enter password
 3. Click Log In</t>
   </si>
   <si>
-    <t xml:space="preserve">username=(blank) / password=demo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation/error message shown; login blocked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.name("username"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOG-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login fails with empty password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter username
+    <t>username=(blank) / password=demo</t>
+  </si>
+  <si>
+    <t>Validation/error message shown; login blocked</t>
+  </si>
+  <si>
+    <t>By.name("username"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-LOG-05</t>
+  </si>
+  <si>
+    <t>Login fails with empty password</t>
+  </si>
+  <si>
+    <t>1. Enter username
 2. Leave password blank
 3. Click Log In</t>
   </si>
   <si>
-    <t xml:space="preserve">username=john / password=(blank)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.name("password"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOG-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login fails with both fields empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Leave both fields blank
+    <t>username=john / password=(blank)</t>
+  </si>
+  <si>
+    <t>By.name("password"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-LOG-06</t>
+  </si>
+  <si>
+    <t>Login fails with both fields empty</t>
+  </si>
+  <si>
+    <t>1. Leave both fields blank
 2. Click Log In</t>
   </si>
   <si>
-    <t xml:space="preserve">username=(blank) / password=(blank)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector("input[value='Log In']"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOG-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logout ends session</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is logged in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Log Out' link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redirected to homepage; login panel reappears</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Log Out")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOG-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Forgot login info?' navigates to lookup page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Forgot login info?' link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigates to lookup.htm identity-verification form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOG-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Register' navigates to registration page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Register' link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigates to register.htm registration form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOG-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session persists across internal navigation while logged in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'About Us' in header
+    <t>username=(blank) / password=(blank)</t>
+  </si>
+  <si>
+    <t>By.cssSelector("input[value='Log In']"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-LOG-07</t>
+  </si>
+  <si>
+    <t>Logout ends session</t>
+  </si>
+  <si>
+    <t>User is logged in</t>
+  </si>
+  <si>
+    <t>1. Click 'Log Out' link</t>
+  </si>
+  <si>
+    <t>Redirected to homepage; login panel reappears</t>
+  </si>
+  <si>
+    <t>By.linkText("Log Out")</t>
+  </si>
+  <si>
+    <t>TC-LOG-08</t>
+  </si>
+  <si>
+    <t>'Forgot login info?' navigates to lookup page</t>
+  </si>
+  <si>
+    <t>1. Click 'Forgot login info?' link</t>
+  </si>
+  <si>
+    <t>Navigates to lookup.htm identity-verification form</t>
+  </si>
+  <si>
+    <t>TC-LOG-09</t>
+  </si>
+  <si>
+    <t>'Register' navigates to registration page</t>
+  </si>
+  <si>
+    <t>1. Click 'Register' link</t>
+  </si>
+  <si>
+    <t>Navigates to register.htm registration form</t>
+  </si>
+  <si>
+    <t>TC-LOG-10</t>
+  </si>
+  <si>
+    <t>Session persists across internal navigation while logged in</t>
+  </si>
+  <si>
+    <t>1. Click 'About Us' in header
 2. Return to Home</t>
   </si>
   <si>
-    <t xml:space="preserve">User remains logged in (Log Out link still visible)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("About Us"); By.linkText("Log Out")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration page loads directly via URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to https://parabank.parasoft.com/parabank/register.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page loads (HTTP 200); title equals 'ParaBank | Register for Free Online Account Access'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">driver.getTitle()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All registration form fields are present and editable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration page loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate First Name, Last Name, Address, City, State, Zip Code, Phone, SSN, Username, Password, Confirm Password fields
+    <t>User remains logged in (Log Out link still visible)</t>
+  </si>
+  <si>
+    <t>By.linkText("About Us"); By.linkText("Log Out")</t>
+  </si>
+  <si>
+    <t>TC-REG-01</t>
+  </si>
+  <si>
+    <t>Registration page loads directly via URL</t>
+  </si>
+  <si>
+    <t>1. Navigate to https://parabank.parasoft.com/parabank/register.htm</t>
+  </si>
+  <si>
+    <t>Page loads (HTTP 200); title equals 'ParaBank | Register for Free Online Account Access'</t>
+  </si>
+  <si>
+    <t>driver.getTitle()</t>
+  </si>
+  <si>
+    <t>TC-REG-02</t>
+  </si>
+  <si>
+    <t>All registration form fields are present and editable</t>
+  </si>
+  <si>
+    <t>Registration page loaded</t>
+  </si>
+  <si>
+    <t>1. Locate First Name, Last Name, Address, City, State, Zip Code, Phone, SSN, Username, Password, Confirm Password fields
 2. Locate 'Register' button</t>
   </si>
   <si>
-    <t xml:space="preserve">All 11 fields and the 'Register' button are visible and editable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("customer.firstName"); By.id("customer.lastName"); By.id("customer.address.street"); By.id("customer.address.city"); By.id("customer.address.state"); By.id("customer.address.zipCode"); By.id("customer.phoneNumber"); By.id("customer.ssn"); By.id("customer.username"); By.id("customer.password"); By.id("repeatedPassword"); By.cssSelector("input[value='Register']")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Successful registration with valid, unique data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration page loaded; chosen username does not already exist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill First Name, Last Name, Address, City, State, Zip Code, Phone, SSN
+    <t>All 11 fields and the 'Register' button are visible and editable</t>
+  </si>
+  <si>
+    <t>By.id("customer.firstName"); By.id("customer.lastName"); By.id("customer.address.street"); By.id("customer.address.city"); By.id("customer.address.state"); By.id("customer.address.zipCode"); By.id("customer.phoneNumber"); By.id("customer.ssn"); By.id("customer.username"); By.id("customer.password"); By.id("repeatedPassword"); By.cssSelector("input[value='Register']")</t>
+  </si>
+  <si>
+    <t>TC-REG-03</t>
+  </si>
+  <si>
+    <t>Successful registration with valid, unique data</t>
+  </si>
+  <si>
+    <t>Registration page loaded; chosen username does not already exist</t>
+  </si>
+  <si>
+    <t>1. Fill First Name, Last Name, Address, City, State, Zip Code, Phone, SSN
 2. Enter unique Username
 3. Enter Password and matching Confirm Password
 4. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">firstName=Jane / lastName=Doe / address=123 Main St / city=Springfield / state=IL / zip=62701 / phone=5551234567 / ssn=123-45-6789 / username=janedoe_&lt;timestamp&gt; / password=Passw0rd! / confirm=Passw0rd!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account is created; confirmation message 'Your account was created successfully. You are now logged in.' is shown; user is redirected to accounts overview page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector("input[value='Register']"); By.xpath("//*[contains(text(),'account was created successfully')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newly registered user is automatically logged in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration just completed successfully (see TC-REG-03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify page state immediately after successful registration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Welcome &lt;firstName&gt; &lt;lastName&gt;' and 'Log Out' link are shown; no separate login step required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'Welcome')]"); By.linkText("Log Out")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with all fields empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Leave all fields blank
+    <t>firstName=Jane / lastName=Doe / address=123 Main St / city=Springfield / state=IL / zip=62701 / phone=5551234567 / ssn=123-45-6789 / username=janedoe_&lt;timestamp&gt; / password=Passw0rd! / confirm=Passw0rd!</t>
+  </si>
+  <si>
+    <t>Account is created; confirmation message 'Your account was created successfully. You are now logged in.' is shown; user is redirected to accounts overview page</t>
+  </si>
+  <si>
+    <t>By.cssSelector("input[value='Register']"); By.xpath("//*[contains(text(),'account was created successfully')]")</t>
+  </si>
+  <si>
+    <t>TC-REG-04</t>
+  </si>
+  <si>
+    <t>Newly registered user is automatically logged in</t>
+  </si>
+  <si>
+    <t>Registration just completed successfully (see TC-REG-03)</t>
+  </si>
+  <si>
+    <t>1. Verify page state immediately after successful registration</t>
+  </si>
+  <si>
+    <t>'Welcome &lt;firstName&gt; &lt;lastName&gt;' and 'Log Out' link are shown; no separate login step required</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'Welcome')]"); By.linkText("Log Out")</t>
+  </si>
+  <si>
+    <t>TC-REG-05</t>
+  </si>
+  <si>
+    <t>Registration fails with all fields empty</t>
+  </si>
+  <si>
+    <t>1. Leave all fields blank
 2. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">All fields = (blank)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation errors shown for every required field; account is not created; user stays on registration page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector("input[value='Register']"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with missing First Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields except First Name
+    <t>All fields = (blank)</t>
+  </si>
+  <si>
+    <t>Validation errors shown for every required field; account is not created; user stays on registration page</t>
+  </si>
+  <si>
+    <t>By.cssSelector("input[value='Register']"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-06</t>
+  </si>
+  <si>
+    <t>Registration fails with missing First Name</t>
+  </si>
+  <si>
+    <t>1. Fill all fields except First Name
 2. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">firstName=(blank), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'First name is required.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("customer.firstName"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with missing Last Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields except Last Name
+    <t>firstName=(blank), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'First name is required.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>By.id("customer.firstName"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-07</t>
+  </si>
+  <si>
+    <t>Registration fails with missing Last Name</t>
+  </si>
+  <si>
+    <t>1. Fill all fields except Last Name
 2. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">lastName=(blank), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'Last name is required.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("customer.lastName"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with missing Address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields except Address
+    <t>lastName=(blank), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'Last name is required.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>By.id("customer.lastName"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-08</t>
+  </si>
+  <si>
+    <t>Registration fails with missing Address</t>
+  </si>
+  <si>
+    <t>1. Fill all fields except Address
 2. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">address=(blank), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'Address is required.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("customer.address.street"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with missing City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields except City
+    <t>address=(blank), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'Address is required.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>By.id("customer.address.street"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-09</t>
+  </si>
+  <si>
+    <t>Registration fails with missing City</t>
+  </si>
+  <si>
+    <t>1. Fill all fields except City
 2. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">city=(blank), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'City is required.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("customer.address.city"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with missing State</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields except State
+    <t>city=(blank), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'City is required.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>By.id("customer.address.city"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-10</t>
+  </si>
+  <si>
+    <t>Registration fails with missing State</t>
+  </si>
+  <si>
+    <t>1. Fill all fields except State
 2. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">state=(blank), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'State is required.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("customer.address.state"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with missing Zip Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields except Zip Code
+    <t>state=(blank), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'State is required.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>By.id("customer.address.state"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-11</t>
+  </si>
+  <si>
+    <t>Registration fails with missing Zip Code</t>
+  </si>
+  <si>
+    <t>1. Fill all fields except Zip Code
 2. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">zip=(blank), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'Zip Code is required.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("customer.address.zipCode"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with missing Phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields except Phone
+    <t>zip=(blank), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'Zip Code is required.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>By.id("customer.address.zipCode"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-12</t>
+  </si>
+  <si>
+    <t>Registration fails with missing Phone</t>
+  </si>
+  <si>
+    <t>1. Fill all fields except Phone
 2. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">phone=(blank), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'Phone is required.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("customer.phoneNumber"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with missing SSN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields except SSN
+    <t>phone=(blank), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'Phone is required.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>By.id("customer.phoneNumber"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-13</t>
+  </si>
+  <si>
+    <t>Registration fails with missing SSN</t>
+  </si>
+  <si>
+    <t>1. Fill all fields except SSN
 2. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">ssn=(blank), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'Social security number is required.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("customer.ssn"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with missing Username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields except Username
+    <t>ssn=(blank), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'Social security number is required.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>By.id("customer.ssn"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-14</t>
+  </si>
+  <si>
+    <t>Registration fails with missing Username</t>
+  </si>
+  <si>
+    <t>1. Fill all fields except Username
 2. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">username=(blank), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'Username is required.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("customer.username"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with missing Password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields except Password
+    <t>username=(blank), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'Username is required.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>By.id("customer.username"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-15</t>
+  </si>
+  <si>
+    <t>Registration fails with missing Password</t>
+  </si>
+  <si>
+    <t>1. Fill all fields except Password
 2. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">password=(blank), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'Password is required.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("customer.password"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails with missing Confirm Password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields including Password
+    <t>password=(blank), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'Password is required.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>By.id("customer.password"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-16</t>
+  </si>
+  <si>
+    <t>Registration fails with missing Confirm Password</t>
+  </si>
+  <si>
+    <t>1. Fill all fields including Password
 2. Leave Confirm Password blank
 3. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">confirm=(blank), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'Please confirm your password.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("repeatedPassword"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails when Password and Confirm Password do not match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields
+    <t>confirm=(blank), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'Please confirm your password.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>By.id("repeatedPassword"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-REG-17</t>
+  </si>
+  <si>
+    <t>Registration fails when Password and Confirm Password do not match</t>
+  </si>
+  <si>
+    <t>1. Fill all fields
 2. Enter Password
 3. Enter a different value in Confirm Password
 4. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">password=Passw0rd! / confirm=Different1!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'Passwords did not match.' shown; account is not created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration fails when Username already exists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration page loaded; supplied username belongs to an existing customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill all fields with valid data
+    <t>password=Passw0rd! / confirm=Different1!</t>
+  </si>
+  <si>
+    <t>Validation error 'Passwords did not match.' shown; account is not created</t>
+  </si>
+  <si>
+    <t>TC-REG-18</t>
+  </si>
+  <si>
+    <t>Registration fails when Username already exists</t>
+  </si>
+  <si>
+    <t>Registration page loaded; supplied username belongs to an existing customer</t>
+  </si>
+  <si>
+    <t>1. Fill all fields with valid data
 2. Enter a Username that is already registered
 3. Click 'Register'</t>
   </si>
   <si>
-    <t xml:space="preserve">username=john (existing), all other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error 'This username already exists.' shown; account is not created; user stays on registration page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-REG-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header and footer render correctly on this page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify header nav and footer nav are present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header/footer identical to other pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("headerPanel"); By.id("footerPanel")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HDR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'About Us' header link navigates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any ParaBank page loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'About Us' in top nav</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigates to https://parabank.parasoft.com/parabank/about.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("About Us")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HDR-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Services' header link navigates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Services' in top nav</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigates to https://parabank.parasoft.com/parabank/services.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Services")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HDR-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Products' header link navigates correctly (external)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Products' in top nav</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens https://www.parasoft.com/products/ (external Parasoft site)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Products")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HDR-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Locations' header link navigates correctly (external)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Locations' in top nav</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens https://www.parasoft.com/solutions/ (external Parasoft site)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Locations")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HDR-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Admin Page' header link navigates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Admin Page' in top nav</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigates to https://parabank.parasoft.com/parabank/admin.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Admin Page")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HDR-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'home' secondary link navigates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'home' link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigates to index.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("home")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HDR-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'about' secondary link navigates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'about' link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigates to about.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("about")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HDR-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'contact' secondary link navigates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'contact' link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigates to contact.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("contact")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-HDR-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header links remain identical/present across all internal pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigate through About/Services/Contact/Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify all 6 top-nav items render identically on each page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header nav is consistent site-wide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FTR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Home' footer link navigates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Scroll to footer
+    <t>username=john (existing), all other fields valid</t>
+  </si>
+  <si>
+    <t>Validation error 'This username already exists.' shown; account is not created; user stays on registration page</t>
+  </si>
+  <si>
+    <t>TC-REG-19</t>
+  </si>
+  <si>
+    <t>Header and footer render correctly on this page</t>
+  </si>
+  <si>
+    <t>1. Verify header nav and footer nav are present</t>
+  </si>
+  <si>
+    <t>Header/footer identical to other pages</t>
+  </si>
+  <si>
+    <t>By.id("headerPanel"); By.id("footerPanel")</t>
+  </si>
+  <si>
+    <t>TC-HDR-01</t>
+  </si>
+  <si>
+    <t>'About Us' header link navigates correctly</t>
+  </si>
+  <si>
+    <t>Any ParaBank page loaded</t>
+  </si>
+  <si>
+    <t>1. Click 'About Us' in top nav</t>
+  </si>
+  <si>
+    <t>Navigates to https://parabank.parasoft.com/parabank/about.htm</t>
+  </si>
+  <si>
+    <t>By.linkText("About Us")</t>
+  </si>
+  <si>
+    <t>TC-HDR-02</t>
+  </si>
+  <si>
+    <t>'Services' header link navigates correctly</t>
+  </si>
+  <si>
+    <t>1. Click 'Services' in top nav</t>
+  </si>
+  <si>
+    <t>Navigates to https://parabank.parasoft.com/parabank/services.htm</t>
+  </si>
+  <si>
+    <t>By.linkText("Services")</t>
+  </si>
+  <si>
+    <t>TC-HDR-03</t>
+  </si>
+  <si>
+    <t>'Products' header link navigates correctly (external)</t>
+  </si>
+  <si>
+    <t>1. Click 'Products' in top nav</t>
+  </si>
+  <si>
+    <t>Opens https://www.parasoft.com/products/ (external Parasoft site)</t>
+  </si>
+  <si>
+    <t>By.linkText("Products")</t>
+  </si>
+  <si>
+    <t>TC-HDR-04</t>
+  </si>
+  <si>
+    <t>'Locations' header link navigates correctly (external)</t>
+  </si>
+  <si>
+    <t>1. Click 'Locations' in top nav</t>
+  </si>
+  <si>
+    <t>Opens https://www.parasoft.com/solutions/ (external Parasoft site)</t>
+  </si>
+  <si>
+    <t>By.linkText("Locations")</t>
+  </si>
+  <si>
+    <t>TC-HDR-05</t>
+  </si>
+  <si>
+    <t>'Admin Page' header link navigates correctly</t>
+  </si>
+  <si>
+    <t>1. Click 'Admin Page' in top nav</t>
+  </si>
+  <si>
+    <t>Navigates to https://parabank.parasoft.com/parabank/admin.htm</t>
+  </si>
+  <si>
+    <t>By.linkText("Admin Page")</t>
+  </si>
+  <si>
+    <t>TC-HDR-06</t>
+  </si>
+  <si>
+    <t>'home' secondary link navigates correctly</t>
+  </si>
+  <si>
+    <t>1. Click 'home' link</t>
+  </si>
+  <si>
+    <t>Navigates to index.htm</t>
+  </si>
+  <si>
+    <t>By.linkText("home")</t>
+  </si>
+  <si>
+    <t>TC-HDR-07</t>
+  </si>
+  <si>
+    <t>'about' secondary link navigates correctly</t>
+  </si>
+  <si>
+    <t>1. Click 'about' link</t>
+  </si>
+  <si>
+    <t>Navigates to about.htm</t>
+  </si>
+  <si>
+    <t>By.linkText("about")</t>
+  </si>
+  <si>
+    <t>TC-HDR-08</t>
+  </si>
+  <si>
+    <t>'contact' secondary link navigates correctly</t>
+  </si>
+  <si>
+    <t>1. Click 'contact' link</t>
+  </si>
+  <si>
+    <t>Navigates to contact.htm</t>
+  </si>
+  <si>
+    <t>By.linkText("contact")</t>
+  </si>
+  <si>
+    <t>TC-HDR-09</t>
+  </si>
+  <si>
+    <t>Header links remain identical/present across all internal pages</t>
+  </si>
+  <si>
+    <t>Navigate through About/Services/Contact/Admin</t>
+  </si>
+  <si>
+    <t>1. Verify all 6 top-nav items render identically on each page</t>
+  </si>
+  <si>
+    <t>Header nav is consistent site-wide</t>
+  </si>
+  <si>
+    <t>TC-FTR-01</t>
+  </si>
+  <si>
+    <t>'Home' footer link navigates correctly</t>
+  </si>
+  <si>
+    <t>1. Scroll to footer
 2. Click 'Home'</t>
   </si>
   <si>
-    <t xml:space="preserve">By.linkText("Home")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FTR-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'About Us' footer link navigates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'About Us' in footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector("#footerPanel a[href*='about.htm']")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FTR-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Services' footer link navigates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Services' in footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigates to services.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector("#footerPanel a[href*='services.htm']")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FTR-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Products' footer link navigates correctly (external)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Products' in footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens https://www.parasoft.com/products/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector("#footerPanel a[href*='products']")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FTR-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Locations' footer link navigates correctly (external)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Locations' in footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens https://www.parasoft.com/solutions/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector("#footerPanel a[href*='contacts']")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FTR-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Forum' footer link navigates correctly (external)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Forum' in footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens https://forums.parasoft.com/ in a working state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Forum")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FTR-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Site Map' footer link navigates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Site Map' in footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigates to sitemap.htm; all site links listed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Site Map")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FTR-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Contact Us' footer link navigates correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Contact Us' in footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Contact Us")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FTR-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copyright text is visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify footer copyright line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'© Parasoft. All rights reserved.' is visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'Parasoft. All rights reserved.')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FTR-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'www.parasoft.com' footer link navigates correctly (external)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'www.parasoft.com' under 'Visit us at:'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens https://www.parasoft.com/ main marketing site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("www.parasoft.com")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FTR-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Footer is present and identical on every page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigate through Home/About/Services/Contact/Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify footer links render identically on each page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Footer is consistent across the whole site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.id("footerPanel")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ABT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About Us page loads directly via URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to https://parabank.parasoft.com/parabank/about.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page loads; title equals 'ParaBank | About Us'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ABT-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'ParaSoft Demo Website' heading is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About Us page loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate page heading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heading 'ParaSoft Demo Website' is visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//h1[contains(text(),'ParaSoft Demo Website')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ABT-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disclaimer text is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate body paragraph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text stating ParaBank is a demo site / 'not a real bank' is visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'not a real bank')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ABT-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parasoft external link is present and correct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'www.parasoft.com' link in body text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link points to https://www.parasoft.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.partialLinkText("www.parasoft.com")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ABT-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone contact number is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate phone number text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'888-305-0041' is visible on the page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'888-305-0041')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ABT-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-SVC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Services page loads directly via URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to https://parabank.parasoft.com/parabank/services.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page loads; title equals 'ParaBank | Services'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-SVC-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bookstore SOAP services table renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Services page loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Available Bookstore SOAP services' table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table lists Bookstore, Bookstore v2.0, and WS-Security variants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'Available Bookstore SOAP services')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-SVC-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bookstore WSDL link is clickable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click WSDL link for 'Bookstore' service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens the WSDL XML document (store-01?wsdl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.partialLinkText("WSDL")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-SVC-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ParaBank SOAP services table renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Available ParaBank SOAP services' table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LoanProcessorService and ParaBankService entries listed with WSDL links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'Available ParaBank SOAP services')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-SVC-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ParaBank services method table renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate ParaBank services methods table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Methods (getAccount, login, deposit, withdraw, transfer, etc.) listed with parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'getAccount')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-SVC-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESTful services section renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Available RESTful services' section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endpoint address, WADL and OpenAPI links are visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.partialLinkText("OpenAPI")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-SVC-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-CNT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact Us page loads directly via URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to https://parabank.parasoft.com/parabank/contact.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page loads; title equals 'ParaBank | Customer Care'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-CNT-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Care form fields are present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact Us page loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate Name, Email, Phone, Message fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All four fields are visible and editable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.name("name"); By.name("email"); By.name("phone"); By.name("message")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-CNT-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit form with valid data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill Name, Email, Phone, Message
+    <t>By.linkText("Home")</t>
+  </si>
+  <si>
+    <t>TC-FTR-02</t>
+  </si>
+  <si>
+    <t>'About Us' footer link navigates correctly</t>
+  </si>
+  <si>
+    <t>1. Click 'About Us' in footer</t>
+  </si>
+  <si>
+    <t>By.cssSelector("#footerPanel a[href*='about.htm']")</t>
+  </si>
+  <si>
+    <t>TC-FTR-03</t>
+  </si>
+  <si>
+    <t>'Services' footer link navigates correctly</t>
+  </si>
+  <si>
+    <t>1. Click 'Services' in footer</t>
+  </si>
+  <si>
+    <t>Navigates to services.htm</t>
+  </si>
+  <si>
+    <t>By.cssSelector("#footerPanel a[href*='services.htm']")</t>
+  </si>
+  <si>
+    <t>TC-FTR-04</t>
+  </si>
+  <si>
+    <t>'Products' footer link navigates correctly (external)</t>
+  </si>
+  <si>
+    <t>1. Click 'Products' in footer</t>
+  </si>
+  <si>
+    <t>Opens https://www.parasoft.com/products/</t>
+  </si>
+  <si>
+    <t>By.cssSelector("#footerPanel a[href*='products']")</t>
+  </si>
+  <si>
+    <t>TC-FTR-05</t>
+  </si>
+  <si>
+    <t>'Locations' footer link navigates correctly (external)</t>
+  </si>
+  <si>
+    <t>1. Click 'Locations' in footer</t>
+  </si>
+  <si>
+    <t>Opens https://www.parasoft.com/solutions/</t>
+  </si>
+  <si>
+    <t>By.cssSelector("#footerPanel a[href*='contacts']")</t>
+  </si>
+  <si>
+    <t>TC-FTR-06</t>
+  </si>
+  <si>
+    <t>'Forum' footer link navigates correctly (external)</t>
+  </si>
+  <si>
+    <t>1. Click 'Forum' in footer</t>
+  </si>
+  <si>
+    <t>Opens https://forums.parasoft.com/ in a working state</t>
+  </si>
+  <si>
+    <t>By.linkText("Forum")</t>
+  </si>
+  <si>
+    <t>TC-FTR-07</t>
+  </si>
+  <si>
+    <t>'Site Map' footer link navigates correctly</t>
+  </si>
+  <si>
+    <t>1. Click 'Site Map' in footer</t>
+  </si>
+  <si>
+    <t>Navigates to sitemap.htm; all site links listed</t>
+  </si>
+  <si>
+    <t>By.linkText("Site Map")</t>
+  </si>
+  <si>
+    <t>TC-FTR-08</t>
+  </si>
+  <si>
+    <t>'Contact Us' footer link navigates correctly</t>
+  </si>
+  <si>
+    <t>1. Click 'Contact Us' in footer</t>
+  </si>
+  <si>
+    <t>By.linkText("Contact Us")</t>
+  </si>
+  <si>
+    <t>TC-FTR-09</t>
+  </si>
+  <si>
+    <t>Copyright text is visible</t>
+  </si>
+  <si>
+    <t>1. Verify footer copyright line</t>
+  </si>
+  <si>
+    <t>'© Parasoft. All rights reserved.' is visible</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'Parasoft. All rights reserved.')]")</t>
+  </si>
+  <si>
+    <t>TC-FTR-10</t>
+  </si>
+  <si>
+    <t>'www.parasoft.com' footer link navigates correctly (external)</t>
+  </si>
+  <si>
+    <t>1. Click 'www.parasoft.com' under 'Visit us at:'</t>
+  </si>
+  <si>
+    <t>Opens https://www.parasoft.com/ main marketing site</t>
+  </si>
+  <si>
+    <t>By.linkText("www.parasoft.com")</t>
+  </si>
+  <si>
+    <t>TC-FTR-11</t>
+  </si>
+  <si>
+    <t>Footer is present and identical on every page</t>
+  </si>
+  <si>
+    <t>Navigate through Home/About/Services/Contact/Admin</t>
+  </si>
+  <si>
+    <t>1. Verify footer links render identically on each page</t>
+  </si>
+  <si>
+    <t>Footer is consistent across the whole site</t>
+  </si>
+  <si>
+    <t>By.id("footerPanel")</t>
+  </si>
+  <si>
+    <t>TC-ABT-01</t>
+  </si>
+  <si>
+    <t>About Us page loads directly via URL</t>
+  </si>
+  <si>
+    <t>1. Navigate to https://parabank.parasoft.com/parabank/about.htm</t>
+  </si>
+  <si>
+    <t>Page loads; title equals 'ParaBank | About Us'</t>
+  </si>
+  <si>
+    <t>TC-ABT-02</t>
+  </si>
+  <si>
+    <t>'ParaSoft Demo Website' heading is displayed</t>
+  </si>
+  <si>
+    <t>About Us page loaded</t>
+  </si>
+  <si>
+    <t>1. Locate page heading</t>
+  </si>
+  <si>
+    <t>Heading 'ParaSoft Demo Website' is visible</t>
+  </si>
+  <si>
+    <t>By.xpath("//h1[contains(text(),'ParaSoft Demo Website')]")</t>
+  </si>
+  <si>
+    <t>TC-ABT-03</t>
+  </si>
+  <si>
+    <t>Disclaimer text is displayed</t>
+  </si>
+  <si>
+    <t>1. Locate body paragraph</t>
+  </si>
+  <si>
+    <t>Text stating ParaBank is a demo site / 'not a real bank' is visible</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'not a real bank')]")</t>
+  </si>
+  <si>
+    <t>TC-ABT-04</t>
+  </si>
+  <si>
+    <t>Parasoft external link is present and correct</t>
+  </si>
+  <si>
+    <t>1. Locate 'www.parasoft.com' link in body text</t>
+  </si>
+  <si>
+    <t>Link points to https://www.parasoft.com/</t>
+  </si>
+  <si>
+    <t>By.partialLinkText("www.parasoft.com")</t>
+  </si>
+  <si>
+    <t>TC-ABT-05</t>
+  </si>
+  <si>
+    <t>Phone contact number is displayed</t>
+  </si>
+  <si>
+    <t>1. Locate phone number text</t>
+  </si>
+  <si>
+    <t>'888-305-0041' is visible on the page</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'888-305-0041')]")</t>
+  </si>
+  <si>
+    <t>TC-ABT-06</t>
+  </si>
+  <si>
+    <t>TC-SVC-01</t>
+  </si>
+  <si>
+    <t>Services page loads directly via URL</t>
+  </si>
+  <si>
+    <t>1. Navigate to https://parabank.parasoft.com/parabank/services.htm</t>
+  </si>
+  <si>
+    <t>Page loads; title equals 'ParaBank | Services'</t>
+  </si>
+  <si>
+    <t>TC-SVC-02</t>
+  </si>
+  <si>
+    <t>Bookstore SOAP services table renders</t>
+  </si>
+  <si>
+    <t>Services page loaded</t>
+  </si>
+  <si>
+    <t>1. Locate 'Available Bookstore SOAP services' table</t>
+  </si>
+  <si>
+    <t>Table lists Bookstore, Bookstore v2.0, and WS-Security variants</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'Available Bookstore SOAP services')]")</t>
+  </si>
+  <si>
+    <t>TC-SVC-03</t>
+  </si>
+  <si>
+    <t>Bookstore WSDL link is clickable</t>
+  </si>
+  <si>
+    <t>1. Click WSDL link for 'Bookstore' service</t>
+  </si>
+  <si>
+    <t>Opens the WSDL XML document (store-01?wsdl)</t>
+  </si>
+  <si>
+    <t>By.partialLinkText("WSDL")</t>
+  </si>
+  <si>
+    <t>TC-SVC-04</t>
+  </si>
+  <si>
+    <t>ParaBank SOAP services table renders</t>
+  </si>
+  <si>
+    <t>1. Locate 'Available ParaBank SOAP services' table</t>
+  </si>
+  <si>
+    <t>LoanProcessorService and ParaBankService entries listed with WSDL links</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'Available ParaBank SOAP services')]")</t>
+  </si>
+  <si>
+    <t>TC-SVC-05</t>
+  </si>
+  <si>
+    <t>ParaBank services method table renders</t>
+  </si>
+  <si>
+    <t>1. Locate ParaBank services methods table</t>
+  </si>
+  <si>
+    <t>Methods (getAccount, login, deposit, withdraw, transfer, etc.) listed with parameters</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'getAccount')]")</t>
+  </si>
+  <si>
+    <t>TC-SVC-06</t>
+  </si>
+  <si>
+    <t>RESTful services section renders</t>
+  </si>
+  <si>
+    <t>1. Locate 'Available RESTful services' section</t>
+  </si>
+  <si>
+    <t>Endpoint address, WADL and OpenAPI links are visible</t>
+  </si>
+  <si>
+    <t>By.partialLinkText("OpenAPI")</t>
+  </si>
+  <si>
+    <t>TC-SVC-07</t>
+  </si>
+  <si>
+    <t>TC-CNT-01</t>
+  </si>
+  <si>
+    <t>Contact Us page loads directly via URL</t>
+  </si>
+  <si>
+    <t>1. Navigate to https://parabank.parasoft.com/parabank/contact.htm</t>
+  </si>
+  <si>
+    <t>Page loads; title equals 'ParaBank | Customer Care'</t>
+  </si>
+  <si>
+    <t>TC-CNT-02</t>
+  </si>
+  <si>
+    <t>Customer Care form fields are present</t>
+  </si>
+  <si>
+    <t>Contact Us page loaded</t>
+  </si>
+  <si>
+    <t>1. Locate Name, Email, Phone, Message fields</t>
+  </si>
+  <si>
+    <t>All four fields are visible and editable</t>
+  </si>
+  <si>
+    <t>By.name("name"); By.name("email"); By.name("phone"); By.name("message")</t>
+  </si>
+  <si>
+    <t>TC-CNT-03</t>
+  </si>
+  <si>
+    <t>Submit form with valid data</t>
+  </si>
+  <si>
+    <t>1. Fill Name, Email, Phone, Message
 2. Click 'Send to Customer Care'</t>
   </si>
   <si>
-    <t xml:space="preserve">name=John Smith / email=john@test.com / phone=1234567890 / message=Test inquiry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmation page/message is shown (e.g. 'Thank you...')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.name("name"); By.name("email"); By.name("phone"); By.name("message"); By.cssSelector("input[value='Send to Customer Care']")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-CNT-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit form with all fields empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Leave all fields blank
+    <t>name=John Smith / email=john@test.com / phone=1234567890 / message=Test inquiry</t>
+  </si>
+  <si>
+    <t>Confirmation page/message is shown (e.g. 'Thank you...')</t>
+  </si>
+  <si>
+    <t>By.name("name"); By.name("email"); By.name("phone"); By.name("message"); By.cssSelector("input[value='Send to Customer Care']")</t>
+  </si>
+  <si>
+    <t>TC-CNT-04</t>
+  </si>
+  <si>
+    <t>Submit form with all fields empty</t>
+  </si>
+  <si>
+    <t>1. Leave all fields blank
 2. Click 'Send to Customer Care'</t>
   </si>
   <si>
-    <t xml:space="preserve">Validation errors shown for required fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector("input[value='Send to Customer Care']"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-CNT-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit form with invalid email format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill Name, Phone, Message
+    <t>Validation errors shown for required fields</t>
+  </si>
+  <si>
+    <t>By.cssSelector("input[value='Send to Customer Care']"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-CNT-05</t>
+  </si>
+  <si>
+    <t>Submit form with invalid email format</t>
+  </si>
+  <si>
+    <t>1. Fill Name, Phone, Message
 2. Enter invalid email
 3. Submit</t>
   </si>
   <si>
-    <t xml:space="preserve">email=not-an-email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error or rejection shown for email field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.name("email"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-CNT-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit form with missing message only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Fill Name, Email, Phone
+    <t>email=not-an-email</t>
+  </si>
+  <si>
+    <t>Validation error or rejection shown for email field</t>
+  </si>
+  <si>
+    <t>By.name("email"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-CNT-06</t>
+  </si>
+  <si>
+    <t>Submit form with missing message only</t>
+  </si>
+  <si>
+    <t>1. Fill Name, Email, Phone
 2. Leave Message blank
 3. Submit</t>
   </si>
   <si>
-    <t xml:space="preserve">message=(blank)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation error shown for Message field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.name("message"); By.cssSelector(".error")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-CNT-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ADM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin page loads directly via URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to https://parabank.parasoft.com/parabank/admin.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page loads; title equals 'ParaBank | Administration'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ADM-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Initialize' database button is present and functional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin page loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Initialize' button under Database section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database is reset to a populated state; confirmation/status shown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector("input[value='Initialize']")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ADM-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Clean' database button is present and functional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Clean' button under Database section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database is reset to a minimal state; confirmation/status shown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector("input[value='Clean']")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ADM-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JMS Service status is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Status' field under JMS Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status shows 'Running'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'Running')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ADM-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Access Mode radio options render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate SOAP / REST(XML) / REST(JSON) / JDBC radio buttons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All 4 options are present; JDBC marked as default</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.name("dataAccessMode")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ADM-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Web Service WSDL/WADL/OpenAPI links render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate ParaBank Service links (WSDL, WADL, OpenAPI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All three links are present and point to valid endpoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.partialLinkText("WSDL"); By.partialLinkText("WADL"); By.partialLinkText("OpenAPI")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ADM-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Settings fields render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate Init. Balance, Min. Balance, Loan Provider, Loan Processor, Threshold fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All settings fields/controls are visible and editable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.name("initialBalance"); By.name("minimumBalance"); By.name("loanProvider"); By.name("loanProcessor"); By.name("threshold")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-ADM-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-PRD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Products page loads via header/footer link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Products' link (header or footer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens https://www.parasoft.com/products/ successfully (HTTP 200)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-PRD-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Products page title and hero heading render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Products page loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify page title and 'Find the Testing Solution That Fits Your Team Perfectly' heading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title contains 'Automated Software Testing Tools'; hero heading visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">driver.getTitle(); By.tagName("h1")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-PRD-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product cards (Jtest, SOAtest, Selenic, etc.) render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Most Popular Products' grid
+    <t>message=(blank)</t>
+  </si>
+  <si>
+    <t>Validation error shown for Message field</t>
+  </si>
+  <si>
+    <t>By.name("message"); By.cssSelector(".error")</t>
+  </si>
+  <si>
+    <t>TC-CNT-07</t>
+  </si>
+  <si>
+    <t>TC-ADM-01</t>
+  </si>
+  <si>
+    <t>Admin page loads directly via URL</t>
+  </si>
+  <si>
+    <t>1. Navigate to https://parabank.parasoft.com/parabank/admin.htm</t>
+  </si>
+  <si>
+    <t>Page loads; title equals 'ParaBank | Administration'</t>
+  </si>
+  <si>
+    <t>TC-ADM-02</t>
+  </si>
+  <si>
+    <t>'Initialize' database button is present and functional</t>
+  </si>
+  <si>
+    <t>Admin page loaded</t>
+  </si>
+  <si>
+    <t>1. Click 'Initialize' button under Database section</t>
+  </si>
+  <si>
+    <t>Database is reset to a populated state; confirmation/status shown</t>
+  </si>
+  <si>
+    <t>By.cssSelector("input[value='Initialize']")</t>
+  </si>
+  <si>
+    <t>TC-ADM-03</t>
+  </si>
+  <si>
+    <t>'Clean' database button is present and functional</t>
+  </si>
+  <si>
+    <t>1. Click 'Clean' button under Database section</t>
+  </si>
+  <si>
+    <t>Database is reset to a minimal state; confirmation/status shown</t>
+  </si>
+  <si>
+    <t>By.cssSelector("input[value='Clean']")</t>
+  </si>
+  <si>
+    <t>TC-ADM-04</t>
+  </si>
+  <si>
+    <t>JMS Service status is displayed</t>
+  </si>
+  <si>
+    <t>1. Locate 'Status' field under JMS Service</t>
+  </si>
+  <si>
+    <t>Status shows 'Running'</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'Running')]")</t>
+  </si>
+  <si>
+    <t>TC-ADM-05</t>
+  </si>
+  <si>
+    <t>Data Access Mode radio options render</t>
+  </si>
+  <si>
+    <t>1. Locate SOAP / REST(XML) / REST(JSON) / JDBC radio buttons</t>
+  </si>
+  <si>
+    <t>All 4 options are present; JDBC marked as default</t>
+  </si>
+  <si>
+    <t>By.name("dataAccessMode")</t>
+  </si>
+  <si>
+    <t>TC-ADM-06</t>
+  </si>
+  <si>
+    <t>Web Service WSDL/WADL/OpenAPI links render</t>
+  </si>
+  <si>
+    <t>1. Locate ParaBank Service links (WSDL, WADL, OpenAPI)</t>
+  </si>
+  <si>
+    <t>All three links are present and point to valid endpoints</t>
+  </si>
+  <si>
+    <t>By.partialLinkText("WSDL"); By.partialLinkText("WADL"); By.partialLinkText("OpenAPI")</t>
+  </si>
+  <si>
+    <t>TC-ADM-07</t>
+  </si>
+  <si>
+    <t>Application Settings fields render</t>
+  </si>
+  <si>
+    <t>1. Locate Init. Balance, Min. Balance, Loan Provider, Loan Processor, Threshold fields</t>
+  </si>
+  <si>
+    <t>All settings fields/controls are visible and editable</t>
+  </si>
+  <si>
+    <t>By.name("initialBalance"); By.name("minimumBalance"); By.name("loanProvider"); By.name("loanProcessor"); By.name("threshold")</t>
+  </si>
+  <si>
+    <t>TC-ADM-08</t>
+  </si>
+  <si>
+    <t>TC-PRD-01</t>
+  </si>
+  <si>
+    <t>Products page loads via header/footer link</t>
+  </si>
+  <si>
+    <t>1. Click 'Products' link (header or footer)</t>
+  </si>
+  <si>
+    <t>Opens https://www.parasoft.com/products/ successfully (HTTP 200)</t>
+  </si>
+  <si>
+    <t>TC-PRD-02</t>
+  </si>
+  <si>
+    <t>Products page title and hero heading render</t>
+  </si>
+  <si>
+    <t>Products page loaded</t>
+  </si>
+  <si>
+    <t>1. Verify page title and 'Find the Testing Solution That Fits Your Team Perfectly' heading</t>
+  </si>
+  <si>
+    <t>Title contains 'Automated Software Testing Tools'; hero heading visible</t>
+  </si>
+  <si>
+    <t>driver.getTitle(); By.tagName("h1")</t>
+  </si>
+  <si>
+    <t>TC-PRD-03</t>
+  </si>
+  <si>
+    <t>Product cards (Jtest, SOAtest, Selenic, etc.) render</t>
+  </si>
+  <si>
+    <t>1. Locate 'Most Popular Products' grid
 2. Verify product cards render with name + 'Learn More' link</t>
   </si>
   <si>
-    <t xml:space="preserve">At least 5 product cards are visible, each with a working 'Learn More' link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.partialLinkText("Learn More")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-PRD-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top navigation (Products/Solutions/Industries/etc.) is present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify main nav menu renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Products, Solutions, Industries, Customer Success, Resources, Contact Us all visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.tagName("nav")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-PRD-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Contact Us' CTA on Products page works</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Contact Us' link/button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigates to https://www.parasoft.com/contact/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Locations page loads via header/footer link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Locations' link (header or footer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens https://www.parasoft.com/solutions/ successfully (HTTP 200)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOC-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solutions page title and hero heading render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Locations/Solutions page loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify page title and hero heading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title contains 'Automated Software Testing Solutions'; hero heading visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOC-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'By Capability' / 'By Industry' / 'By Compliance Standard' anchor links work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click each in-page anchor link
+    <t>At least 5 product cards are visible, each with a working 'Learn More' link</t>
+  </si>
+  <si>
+    <t>By.partialLinkText("Learn More")</t>
+  </si>
+  <si>
+    <t>TC-PRD-04</t>
+  </si>
+  <si>
+    <t>Top navigation (Products/Solutions/Industries/etc.) is present</t>
+  </si>
+  <si>
+    <t>1. Verify main nav menu renders</t>
+  </si>
+  <si>
+    <t>Products, Solutions, Industries, Customer Success, Resources, Contact Us all visible</t>
+  </si>
+  <si>
+    <t>By.tagName("nav")</t>
+  </si>
+  <si>
+    <t>TC-PRD-05</t>
+  </si>
+  <si>
+    <t>'Contact Us' CTA on Products page works</t>
+  </si>
+  <si>
+    <t>1. Click 'Contact Us' link/button</t>
+  </si>
+  <si>
+    <t>Navigates to https://www.parasoft.com/contact/</t>
+  </si>
+  <si>
+    <t>TC-LOC-01</t>
+  </si>
+  <si>
+    <t>Locations page loads via header/footer link</t>
+  </si>
+  <si>
+    <t>1. Click 'Locations' link (header or footer)</t>
+  </si>
+  <si>
+    <t>Opens https://www.parasoft.com/solutions/ successfully (HTTP 200)</t>
+  </si>
+  <si>
+    <t>TC-LOC-02</t>
+  </si>
+  <si>
+    <t>Solutions page title and hero heading render</t>
+  </si>
+  <si>
+    <t>Locations/Solutions page loaded</t>
+  </si>
+  <si>
+    <t>1. Verify page title and hero heading</t>
+  </si>
+  <si>
+    <t>Title contains 'Automated Software Testing Solutions'; hero heading visible</t>
+  </si>
+  <si>
+    <t>TC-LOC-03</t>
+  </si>
+  <si>
+    <t>'By Capability' / 'By Industry' / 'By Compliance Standard' anchor links work</t>
+  </si>
+  <si>
+    <t>1. Click each in-page anchor link
 2. Verify page scrolls to matching section</t>
   </si>
   <si>
-    <t xml:space="preserve">Each anchor scrolls to the correct section (#capability, #industry, #standard)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("By Capability"); By.linkText("By Industry"); By.linkText("By Compliance Standard")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOC-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compliance standard links (MISRA, OWASP, ISO 26262, etc.) render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Solutions for Every Compliance Need' list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All listed compliance standards are clickable links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.partialLinkText("MISRA")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-LOC-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Contact Us' CTA on Solutions page works</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FRM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forum page loads via footer link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Forum' link in footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens https://forums.parasoft.com/ successfully (HTTP 200)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FRM-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forum homepage title renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forum page loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify page title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title equals 'Home - Parasoft Forums'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FRM-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Featured Categories list renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Featured Categories' section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category links (Product Ideas, Parasoft Products, Jtest, SOAtest, etc.) are visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Product Ideas")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FRM-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recent Discussions list renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Recent Discussions' section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At least 5 discussion threads are listed with clickable titles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.cssSelector(".DataList .Item")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FRM-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Sign In' and 'Register' links render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Welcome!' panel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Sign In' and 'Register' links are visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Sign In"); By.linkText("Register")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-FRM-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Discussions' and 'Categories' top nav work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Discussions'
+    <t>Each anchor scrolls to the correct section (#capability, #industry, #standard)</t>
+  </si>
+  <si>
+    <t>By.linkText("By Capability"); By.linkText("By Industry"); By.linkText("By Compliance Standard")</t>
+  </si>
+  <si>
+    <t>TC-LOC-04</t>
+  </si>
+  <si>
+    <t>Compliance standard links (MISRA, OWASP, ISO 26262, etc.) render</t>
+  </si>
+  <si>
+    <t>1. Locate 'Solutions for Every Compliance Need' list</t>
+  </si>
+  <si>
+    <t>All listed compliance standards are clickable links</t>
+  </si>
+  <si>
+    <t>By.partialLinkText("MISRA")</t>
+  </si>
+  <si>
+    <t>TC-LOC-05</t>
+  </si>
+  <si>
+    <t>'Contact Us' CTA on Solutions page works</t>
+  </si>
+  <si>
+    <t>TC-FRM-01</t>
+  </si>
+  <si>
+    <t>Forum page loads via footer link</t>
+  </si>
+  <si>
+    <t>1. Click 'Forum' link in footer</t>
+  </si>
+  <si>
+    <t>Opens https://forums.parasoft.com/ successfully (HTTP 200)</t>
+  </si>
+  <si>
+    <t>TC-FRM-02</t>
+  </si>
+  <si>
+    <t>Forum homepage title renders</t>
+  </si>
+  <si>
+    <t>Forum page loaded</t>
+  </si>
+  <si>
+    <t>1. Verify page title</t>
+  </si>
+  <si>
+    <t>Title equals 'Home - Parasoft Forums'</t>
+  </si>
+  <si>
+    <t>TC-FRM-03</t>
+  </si>
+  <si>
+    <t>Featured Categories list renders</t>
+  </si>
+  <si>
+    <t>1. Locate 'Featured Categories' section</t>
+  </si>
+  <si>
+    <t>Category links (Product Ideas, Parasoft Products, Jtest, SOAtest, etc.) are visible</t>
+  </si>
+  <si>
+    <t>By.linkText("Product Ideas")</t>
+  </si>
+  <si>
+    <t>TC-FRM-04</t>
+  </si>
+  <si>
+    <t>Recent Discussions list renders</t>
+  </si>
+  <si>
+    <t>1. Locate 'Recent Discussions' section</t>
+  </si>
+  <si>
+    <t>At least 5 discussion threads are listed with clickable titles</t>
+  </si>
+  <si>
+    <t>By.cssSelector(".DataList .Item")</t>
+  </si>
+  <si>
+    <t>TC-FRM-05</t>
+  </si>
+  <si>
+    <t>'Sign In' and 'Register' links render</t>
+  </si>
+  <si>
+    <t>1. Locate 'Welcome!' panel</t>
+  </si>
+  <si>
+    <t>'Sign In' and 'Register' links are visible</t>
+  </si>
+  <si>
+    <t>By.linkText("Sign In"); By.linkText("Register")</t>
+  </si>
+  <si>
+    <t>TC-FRM-06</t>
+  </si>
+  <si>
+    <t>'Discussions' and 'Categories' top nav work</t>
+  </si>
+  <si>
+    <t>1. Click 'Discussions'
 2. Click 'Categories'</t>
   </si>
   <si>
-    <t xml:space="preserve">Each navigates to its respective listing page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.linkText("Discussions"); By.linkText("Categories")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-PSF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parasoft main site loads via footer 'www.parasoft.com' link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'www.parasoft.com' under 'Visit us at:' in footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens https://www.parasoft.com/ successfully (HTTP 200)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-PSF-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main site title and hero heading render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parasoft main site loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title contains 'Automated Testing to Deliver Superior Quality Software'; 'Go Beyond Testing' heading visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-PSF-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary nav (Products/Solutions/Industries/Customer Success/Resources) renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Verify each main nav item is visible and expandable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All primary nav items are visible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-PSF-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Featured Products section renders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate 'Featured Products' section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product cards (C/C++test, Jtest, SOAtest, Virtualize, etc.) render with links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'Featured Products')]")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-PSF-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Contact Us' CTA works</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Contact Us' link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-PSF-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAQ accordion expands/collapses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click a FAQ question (e.g. 'Why Parasoft?')
+    <t>Each navigates to its respective listing page</t>
+  </si>
+  <si>
+    <t>By.linkText("Discussions"); By.linkText("Categories")</t>
+  </si>
+  <si>
+    <t>TC-PSF-01</t>
+  </si>
+  <si>
+    <t>Parasoft main site loads via footer 'www.parasoft.com' link</t>
+  </si>
+  <si>
+    <t>1. Click 'www.parasoft.com' under 'Visit us at:' in footer</t>
+  </si>
+  <si>
+    <t>Opens https://www.parasoft.com/ successfully (HTTP 200)</t>
+  </si>
+  <si>
+    <t>TC-PSF-02</t>
+  </si>
+  <si>
+    <t>Main site title and hero heading render</t>
+  </si>
+  <si>
+    <t>Parasoft main site loaded</t>
+  </si>
+  <si>
+    <t>Title contains 'Automated Testing to Deliver Superior Quality Software'; 'Go Beyond Testing' heading visible</t>
+  </si>
+  <si>
+    <t>TC-PSF-03</t>
+  </si>
+  <si>
+    <t>Primary nav (Products/Solutions/Industries/Customer Success/Resources) renders</t>
+  </si>
+  <si>
+    <t>1. Verify each main nav item is visible and expandable</t>
+  </si>
+  <si>
+    <t>All primary nav items are visible</t>
+  </si>
+  <si>
+    <t>TC-PSF-04</t>
+  </si>
+  <si>
+    <t>Featured Products section renders</t>
+  </si>
+  <si>
+    <t>1. Locate 'Featured Products' section</t>
+  </si>
+  <si>
+    <t>Product cards (C/C++test, Jtest, SOAtest, Virtualize, etc.) render with links</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'Featured Products')]")</t>
+  </si>
+  <si>
+    <t>TC-PSF-05</t>
+  </si>
+  <si>
+    <t>'Contact Us' CTA works</t>
+  </si>
+  <si>
+    <t>1. Click 'Contact Us' link</t>
+  </si>
+  <si>
+    <t>TC-PSF-06</t>
+  </si>
+  <si>
+    <t>FAQ accordion expands/collapses</t>
+  </si>
+  <si>
+    <t>1. Click a FAQ question (e.g. 'Why Parasoft?')
 2. Verify it expands
 3. Click again to collapse</t>
   </si>
   <si>
-    <t xml:space="preserve">Accordion toggles open/closed correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By.xpath("//*[contains(text(),'Why Parasoft?')]")</t>
+    <t>Accordion toggles open/closed correctly</t>
+  </si>
+  <si>
+    <t>By.xpath("//*[contains(text(),'Why Parasoft?')]")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1778,39 +1780,21 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1847,14 +1831,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFB7B7B7"/>
       </left>
@@ -1870,114 +1854,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F4E78"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -2036,95 +1938,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -2132,12 +2002,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -2166,7 +2036,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2187,7 +2057,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2238,7 +2108,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2256,33 +2126,32 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="40.44140625" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2311,7 +2180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -2338,7 +2207,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -2365,7 +2234,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -2392,7 +2261,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -2419,7 +2288,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
@@ -2446,7 +2315,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>39</v>
       </c>
@@ -2473,7 +2342,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>44</v>
       </c>
@@ -2500,7 +2369,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
@@ -2527,7 +2396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>54</v>
       </c>
@@ -2554,7 +2423,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>59</v>
       </c>
@@ -2582,38 +2451,29 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I11"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I11" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="37.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="31.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="29.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="4" max="4" width="37.21875" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="29.21875" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2642,7 +2502,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>455</v>
       </c>
@@ -2669,7 +2529,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>459</v>
       </c>
@@ -2696,7 +2556,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>465</v>
       </c>
@@ -2723,7 +2583,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>470</v>
       </c>
@@ -2750,7 +2610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>475</v>
       </c>
@@ -2777,54 +2637,45 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G11" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I6" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="37.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="36.109375" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="6" width="30.44140625" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="37.77734375" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2853,7 +2704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>479</v>
       </c>
@@ -2880,7 +2731,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>483</v>
       </c>
@@ -2907,7 +2758,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>488</v>
       </c>
@@ -2934,7 +2785,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>493</v>
       </c>
@@ -2961,7 +2812,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>498</v>
       </c>
@@ -2988,54 +2839,45 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G11" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I6" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="33.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="31.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="33.21875" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="6" width="31.6640625" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3064,7 +2906,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>500</v>
       </c>
@@ -3091,7 +2933,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>504</v>
       </c>
@@ -3118,7 +2960,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>509</v>
       </c>
@@ -3145,7 +2987,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>514</v>
       </c>
@@ -3172,7 +3014,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>519</v>
       </c>
@@ -3199,7 +3041,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>524</v>
       </c>
@@ -3226,51 +3068,42 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G11" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I7"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I7" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="31.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="36.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="31.5546875" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3299,7 +3132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>529</v>
       </c>
@@ -3326,7 +3159,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>533</v>
       </c>
@@ -3353,7 +3186,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>537</v>
       </c>
@@ -3380,7 +3213,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>541</v>
       </c>
@@ -3407,7 +3240,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>546</v>
       </c>
@@ -3434,7 +3267,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>549</v>
       </c>
@@ -3461,51 +3294,42 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G11" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I7"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I7" xr:uid="{00000000-0009-0000-0000-00000C000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="31.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" customWidth="1"/>
+    <col min="5" max="5" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="40.21875" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3534,7 +3358,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>64</v>
       </c>
@@ -3561,7 +3385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>70</v>
       </c>
@@ -3588,7 +3412,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>76</v>
       </c>
@@ -3615,7 +3439,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>82</v>
       </c>
@@ -3642,7 +3466,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>88</v>
       </c>
@@ -3669,7 +3493,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>93</v>
       </c>
@@ -3696,7 +3520,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>98</v>
       </c>
@@ -3723,7 +3547,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>104</v>
       </c>
@@ -3750,7 +3574,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>108</v>
       </c>
@@ -3777,7 +3601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>112</v>
       </c>
@@ -3805,38 +3629,29 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I11"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I11" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="31.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" customWidth="1"/>
+    <col min="5" max="5" width="99.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="40.21875" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3865,7 +3680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>117</v>
       </c>
@@ -3892,7 +3707,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>122</v>
       </c>
@@ -3919,7 +3734,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>128</v>
       </c>
@@ -3946,7 +3761,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>135</v>
       </c>
@@ -3973,7 +3788,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>141</v>
       </c>
@@ -4000,7 +3815,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>147</v>
       </c>
@@ -4027,7 +3842,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>153</v>
       </c>
@@ -4054,7 +3869,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>159</v>
       </c>
@@ -4081,7 +3896,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>165</v>
       </c>
@@ -4108,7 +3923,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>171</v>
       </c>
@@ -4135,7 +3950,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>177</v>
       </c>
@@ -4162,7 +3977,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>183</v>
       </c>
@@ -4189,7 +4004,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>189</v>
       </c>
@@ -4216,7 +4031,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>195</v>
       </c>
@@ -4243,7 +4058,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>201</v>
       </c>
@@ -4270,7 +4085,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>207</v>
       </c>
@@ -4297,7 +4112,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>213</v>
       </c>
@@ -4324,7 +4139,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>218</v>
       </c>
@@ -4351,7 +4166,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>224</v>
       </c>
@@ -4379,36 +4194,28 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="31.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="6" width="31.88671875" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="22.5546875" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4437,7 +4244,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>229</v>
       </c>
@@ -4464,7 +4271,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>235</v>
       </c>
@@ -4491,7 +4298,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>240</v>
       </c>
@@ -4518,7 +4325,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>245</v>
       </c>
@@ -4545,7 +4352,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>250</v>
       </c>
@@ -4572,7 +4379,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>255</v>
       </c>
@@ -4599,7 +4406,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>260</v>
       </c>
@@ -4626,7 +4433,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>265</v>
       </c>
@@ -4653,7 +4460,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>270</v>
       </c>
@@ -4680,41 +4487,32 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G11" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I10"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I10" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="25.88671875" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="4" max="4" width="36.33203125" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="40.21875" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4743,7 +4541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>275</v>
       </c>
@@ -4770,7 +4568,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>279</v>
       </c>
@@ -4797,7 +4595,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>283</v>
       </c>
@@ -4824,7 +4622,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>288</v>
       </c>
@@ -4851,7 +4649,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>293</v>
       </c>
@@ -4878,7 +4676,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>298</v>
       </c>
@@ -4905,7 +4703,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>303</v>
       </c>
@@ -4932,7 +4730,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>308</v>
       </c>
@@ -4959,7 +4757,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>312</v>
       </c>
@@ -4986,7 +4784,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>317</v>
       </c>
@@ -5013,7 +4811,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>322</v>
       </c>
@@ -5040,37 +4838,28 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I12" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="37.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="39.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="37.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="39.77734375" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5099,7 +4888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>328</v>
       </c>
@@ -5126,7 +4915,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>332</v>
       </c>
@@ -5153,7 +4942,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>338</v>
       </c>
@@ -5180,7 +4969,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>343</v>
       </c>
@@ -5207,7 +4996,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>348</v>
       </c>
@@ -5234,7 +5023,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>353</v>
       </c>
@@ -5261,50 +5050,41 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G11" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I7"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I7" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="37.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="41.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="37.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="41.21875" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5333,7 +5113,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>354</v>
       </c>
@@ -5360,7 +5140,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>358</v>
       </c>
@@ -5387,7 +5167,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>364</v>
       </c>
@@ -5414,7 +5194,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>369</v>
       </c>
@@ -5441,7 +5221,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>374</v>
       </c>
@@ -5468,7 +5248,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>379</v>
       </c>
@@ -5495,7 +5275,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>384</v>
       </c>
@@ -5522,47 +5302,38 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G11" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I8" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="40.44140625" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5591,7 +5362,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>385</v>
       </c>
@@ -5618,7 +5389,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>389</v>
       </c>
@@ -5645,7 +5416,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="78.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>395</v>
       </c>
@@ -5672,7 +5443,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>401</v>
       </c>
@@ -5699,7 +5470,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>406</v>
       </c>
@@ -5726,7 +5497,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>412</v>
       </c>
@@ -5753,7 +5524,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>418</v>
       </c>
@@ -5780,47 +5551,38 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G11" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I8" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="41.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.89"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="41.6640625" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5849,7 +5611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>419</v>
       </c>
@@ -5876,7 +5638,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>423</v>
       </c>
@@ -5903,7 +5665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>429</v>
       </c>
@@ -5930,7 +5692,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>434</v>
       </c>
@@ -5957,7 +5719,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>439</v>
       </c>
@@ -5984,7 +5746,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>444</v>
       </c>
@@ -6011,7 +5773,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>449</v>
       </c>
@@ -6038,7 +5800,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>454</v>
       </c>
@@ -6065,21 +5827,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G11" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I9"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:I9" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/documents/ParaBank_Test_Cases.xlsx
+++ b/documents/ParaBank_Test_Cases.xlsx
@@ -3,14 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DVDSTORE\Desktop\Rawad files\My Own Files\project\qa-project\bank.system\documents\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31A51F0-89E3-47F8-AA84-500F782A21C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{053F5D90-1E26-40B8-900C-4778B7E8A75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-384000" yWindow="-384000" windowWidth="2388" windowHeight="564" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Homepage" sheetId="1" r:id="rId1"/>
@@ -42,6 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Services!$A$1:$I$8</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
+  <oleSize ref="A1:E4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>

--- a/documents/ParaBank_Test_Cases.xlsx
+++ b/documents/ParaBank_Test_Cases.xlsx
@@ -3,9 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{053F5D90-1E26-40B8-900C-4778B7E8A75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DVDSTORE\Desktop\Rawad files\My Own Files\project\qa-project\bank.system\documents\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B8C63C-2919-4380-BD75-931C1C61FF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-384000" yWindow="-384000" windowWidth="2388" windowHeight="564" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Homepage" sheetId="1" r:id="rId1"/>
@@ -37,7 +42,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Services!$A$1:$I$8</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <oleSize ref="A1:E4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>

--- a/documents/ParaBank_Test_Cases.xlsx
+++ b/documents/ParaBank_Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DVDSTORE\Desktop\Rawad files\My Own Files\project\qa-project\bank.system\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B8C63C-2919-4380-BD75-931C1C61FF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A15F27A-BC10-4C07-B3A6-20C3A8740570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Homepage" sheetId="1" r:id="rId1"/>

--- a/documents/ParaBank_Test_Cases.xlsx
+++ b/documents/ParaBank_Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DVDSTORE\Desktop\Rawad files\My Own Files\project\qa-project\bank.system\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A15F27A-BC10-4C07-B3A6-20C3A8740570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E493B504-AA00-432A-BCE5-F2D0E329FB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Homepage" sheetId="1" r:id="rId1"/>

--- a/documents/ParaBank_Test_Cases.xlsx
+++ b/documents/ParaBank_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DVDSTORE\Desktop\Rawad files\My Own Files\project\qa-project\bank.system\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E493B504-AA00-432A-BCE5-F2D0E329FB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3333E215-7EB5-4C3E-AACE-6DD0442D7160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="544">
   <si>
     <t>TC ID</t>
   </si>
@@ -425,35 +425,13 @@
     <t>TC-REG-01</t>
   </si>
   <si>
-    <t>Registration page loads directly via URL</t>
-  </si>
-  <si>
-    <t>1. Navigate to https://parabank.parasoft.com/parabank/register.htm</t>
-  </si>
-  <si>
-    <t>Page loads (HTTP 200); title equals 'ParaBank | Register for Free Online Account Access'</t>
-  </si>
-  <si>
     <t>driver.getTitle()</t>
   </si>
   <si>
     <t>TC-REG-02</t>
   </si>
   <si>
-    <t>All registration form fields are present and editable</t>
-  </si>
-  <si>
     <t>Registration page loaded</t>
-  </si>
-  <si>
-    <t>1. Locate First Name, Last Name, Address, City, State, Zip Code, Phone, SSN, Username, Password, Confirm Password fields
-2. Locate 'Register' button</t>
-  </si>
-  <si>
-    <t>All 11 fields and the 'Register' button are visible and editable</t>
-  </si>
-  <si>
-    <t>By.id("customer.firstName"); By.id("customer.lastName"); By.id("customer.address.street"); By.id("customer.address.city"); By.id("customer.address.state"); By.id("customer.address.zipCode"); By.id("customer.phoneNumber"); By.id("customer.ssn"); By.id("customer.username"); By.id("customer.password"); By.id("repeatedPassword"); By.cssSelector("input[value='Register']")</t>
   </si>
   <si>
     <t>TC-REG-03</t>
@@ -727,9 +705,6 @@
     <t>By.id("repeatedPassword"); By.cssSelector(".error")</t>
   </si>
   <si>
-    <t>TC-REG-17</t>
-  </si>
-  <si>
     <t>Registration fails when Password and Confirm Password do not match</t>
   </si>
   <si>
@@ -745,9 +720,6 @@
     <t>Validation error 'Passwords did not match.' shown; account is not created</t>
   </si>
   <si>
-    <t>TC-REG-18</t>
-  </si>
-  <si>
     <t>Registration fails when Username already exists</t>
   </si>
   <si>
@@ -763,9 +735,6 @@
   </si>
   <si>
     <t>Validation error 'This username already exists.' shown; account is not created; user stays on registration page</t>
-  </si>
-  <si>
-    <t>TC-REG-19</t>
   </si>
   <si>
     <t>Header and footer render correctly on this page</t>
@@ -1771,7 +1740,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1795,6 +1764,12 @@
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -2504,26 +2479,26 @@
     </row>
     <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>34</v>
@@ -2531,26 +2506,26 @@
     </row>
     <row r="3" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>23</v>
@@ -2558,26 +2533,26 @@
     </row>
     <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>23</v>
@@ -2585,26 +2560,26 @@
     </row>
     <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>23</v>
@@ -2612,26 +2587,26 @@
     </row>
     <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>23</v>
@@ -2706,26 +2681,26 @@
     </row>
     <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>34</v>
@@ -2733,26 +2708,26 @@
     </row>
     <row r="3" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>23</v>
@@ -2760,26 +2735,26 @@
     </row>
     <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>23</v>
@@ -2787,26 +2762,26 @@
     </row>
     <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>495</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>23</v>
@@ -2814,26 +2789,26 @@
     </row>
     <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>23</v>
@@ -2908,26 +2883,26 @@
     </row>
     <row r="2" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>34</v>
@@ -2935,26 +2910,26 @@
     </row>
     <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>23</v>
@@ -2962,26 +2937,26 @@
     </row>
     <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>23</v>
@@ -2989,26 +2964,26 @@
     </row>
     <row r="5" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>516</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>23</v>
@@ -3016,26 +2991,26 @@
     </row>
     <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>23</v>
@@ -3043,26 +3018,26 @@
     </row>
     <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>23</v>
@@ -3134,26 +3109,26 @@
     </row>
     <row r="2" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>34</v>
@@ -3161,26 +3136,26 @@
     </row>
     <row r="3" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>23</v>
@@ -3188,26 +3163,26 @@
     </row>
     <row r="4" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>23</v>
@@ -3215,26 +3190,26 @@
     </row>
     <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>23</v>
@@ -3242,26 +3217,26 @@
     </row>
     <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>23</v>
@@ -3269,26 +3244,26 @@
     </row>
     <row r="7" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>23</v>
@@ -3685,77 +3660,77 @@
         <v>117</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>34</v>
+        <v>127</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>34</v>
+        <v>133</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>16</v>
@@ -3763,80 +3738,80 @@
     </row>
     <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>16</v>
+        <v>145</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>16</v>
+        <v>151</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>34</v>
@@ -3844,26 +3819,26 @@
     </row>
     <row r="8" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>34</v>
@@ -3871,26 +3846,26 @@
     </row>
     <row r="9" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>34</v>
@@ -3898,26 +3873,26 @@
     </row>
     <row r="10" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>34</v>
@@ -3925,26 +3900,26 @@
     </row>
     <row r="11" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>34</v>
@@ -3952,26 +3927,26 @@
     </row>
     <row r="12" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>34</v>
@@ -3979,26 +3954,26 @@
     </row>
     <row r="13" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>34</v>
@@ -4006,26 +3981,26 @@
     </row>
     <row r="14" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>34</v>
@@ -4033,26 +4008,26 @@
     </row>
     <row r="15" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>34</v>
@@ -4060,140 +4035,63 @@
     </row>
     <row r="16" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>34</v>
+        <v>205</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I18" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
+    <row r="18" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -4246,26 +4144,26 @@
     </row>
     <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>34</v>
@@ -4273,26 +4171,26 @@
     </row>
     <row r="3" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>34</v>
@@ -4300,26 +4198,26 @@
     </row>
     <row r="4" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>34</v>
@@ -4327,26 +4225,26 @@
     </row>
     <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>34</v>
@@ -4354,26 +4252,26 @@
     </row>
     <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>34</v>
@@ -4381,26 +4279,26 @@
     </row>
     <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>23</v>
@@ -4408,26 +4306,26 @@
     </row>
     <row r="8" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>23</v>
@@ -4435,26 +4333,26 @@
     </row>
     <row r="9" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>23</v>
@@ -4462,22 +4360,22 @@
     </row>
     <row r="10" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
@@ -4543,26 +4441,26 @@
     </row>
     <row r="2" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>34</v>
@@ -4570,26 +4468,26 @@
     </row>
     <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>34</v>
@@ -4597,26 +4495,26 @@
     </row>
     <row r="4" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>34</v>
@@ -4624,26 +4522,26 @@
     </row>
     <row r="5" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>34</v>
@@ -4651,26 +4549,26 @@
     </row>
     <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>34</v>
@@ -4678,26 +4576,26 @@
     </row>
     <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>34</v>
@@ -4705,26 +4603,26 @@
     </row>
     <row r="8" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>23</v>
@@ -4732,26 +4630,26 @@
     </row>
     <row r="9" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>34</v>
@@ -4759,26 +4657,26 @@
     </row>
     <row r="10" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>23</v>
@@ -4786,26 +4684,26 @@
     </row>
     <row r="11" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>34</v>
@@ -4813,25 +4711,25 @@
     </row>
     <row r="12" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>23</v>
@@ -4890,26 +4788,26 @@
     </row>
     <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>34</v>
@@ -4917,26 +4815,26 @@
     </row>
     <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>23</v>
@@ -4944,26 +4842,26 @@
     </row>
     <row r="4" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>23</v>
@@ -4971,26 +4869,26 @@
     </row>
     <row r="5" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>23</v>
@@ -4998,26 +4896,26 @@
     </row>
     <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>23</v>
@@ -5025,26 +4923,26 @@
     </row>
     <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>23</v>
@@ -5115,26 +5013,26 @@
     </row>
     <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>34</v>
@@ -5142,26 +5040,26 @@
     </row>
     <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>23</v>
@@ -5169,26 +5067,26 @@
     </row>
     <row r="4" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>23</v>
@@ -5196,26 +5094,26 @@
     </row>
     <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>23</v>
@@ -5223,26 +5121,26 @@
     </row>
     <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>23</v>
@@ -5250,26 +5148,26 @@
     </row>
     <row r="7" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>23</v>
@@ -5277,26 +5175,26 @@
     </row>
     <row r="8" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>23</v>
@@ -5364,26 +5262,26 @@
     </row>
     <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>34</v>
@@ -5391,26 +5289,26 @@
     </row>
     <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>16</v>
@@ -5418,26 +5316,26 @@
     </row>
     <row r="4" spans="1:9" ht="78.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>16</v>
@@ -5445,26 +5343,26 @@
     </row>
     <row r="5" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>34</v>
@@ -5472,26 +5370,26 @@
     </row>
     <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>34</v>
@@ -5499,26 +5397,26 @@
     </row>
     <row r="7" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>23</v>
@@ -5526,26 +5424,26 @@
     </row>
     <row r="8" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>23</v>
@@ -5613,26 +5511,26 @@
     </row>
     <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>34</v>
@@ -5640,26 +5538,26 @@
     </row>
     <row r="3" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>16</v>
@@ -5667,26 +5565,26 @@
     </row>
     <row r="4" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>16</v>
@@ -5694,26 +5592,26 @@
     </row>
     <row r="5" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>23</v>
@@ -5721,26 +5619,26 @@
     </row>
     <row r="6" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>34</v>
@@ -5748,26 +5646,26 @@
     </row>
     <row r="7" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>23</v>
@@ -5775,26 +5673,26 @@
     </row>
     <row r="8" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>34</v>
@@ -5802,26 +5700,26 @@
     </row>
     <row r="9" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>23</v>
